--- a/data/export/2026-09-16-浦东35路.xlsx
+++ b/data/export/2026-09-16-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC29"/>
+  <dimension ref="A1:AC47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -436,7 +436,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
@@ -449,11 +449,11 @@
     <col width="10" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="36" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="22" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>159.0</t>
+          <t>148.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>8/27</t>
+          <t>16/27</t>
         </is>
       </c>
     </row>
@@ -875,29 +875,29 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>147分钟</t>
+          <t>157分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>08:11采样：该车到重点站康沈路秀沿路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数33分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>12/27</t>
         </is>
       </c>
     </row>
@@ -994,27 +994,31 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>159分钟</t>
+          <t>156分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：08:11采样，终点ETA 58分钟</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1022,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1046,33 +1050,37 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>142.0</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>8/27</t>
         </is>
       </c>
     </row>
@@ -1100,12 +1108,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程37%处后消失；随后反向物理轨迹由seq28推进至seq60，推进32站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1133,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1141,10 +1149,18 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>迎春路长柳路</t>
+        </is>
+      </c>
       <c r="R6" s="2" t="inlineStr"/>
       <c r="S6" s="2" t="inlineStr"/>
-      <c r="T6" s="2" t="inlineStr"/>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
           <t>06:36</t>
@@ -1162,7 +1178,7 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
@@ -1172,7 +1188,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1216,27 +1232,31 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>162分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -1244,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1268,33 +1288,37 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>162.0</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>23/27</t>
         </is>
       </c>
     </row>
@@ -1327,29 +1351,29 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>173分钟</t>
+          <t>163分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>08:11采样：该车到重点站迎春路金松路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数81分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1359,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1383,12 +1407,12 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
@@ -1398,22 +1422,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>173.0</t>
+          <t>150.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>14/27</t>
+          <t>18/27</t>
         </is>
       </c>
     </row>
@@ -1451,26 +1475,22 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>161分钟</t>
+          <t>163分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>08:11采样：该车到重点站锦绣路花木路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数76分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：09:31采样，终点ETA 6分钟</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -1478,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1507,7 +1527,7 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
@@ -1517,22 +1537,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>161.0</t>
+          <t>146.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>9/27</t>
+          <t>14/27</t>
         </is>
       </c>
     </row>
@@ -1565,29 +1585,29 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>171分钟</t>
+          <t>168分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>08:11采样：该车到重点站迎春路长柳路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数84分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1597,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1621,12 +1641,12 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
@@ -1636,22 +1656,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>168.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>12/27</t>
+          <t>24/27</t>
         </is>
       </c>
     </row>
@@ -1689,26 +1709,22 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>154分钟</t>
+          <t>158分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>08:11采样：该车到重点站迎春路长柳路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数79分钟，约±9分钟</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：09:20采样，终点ETA 23分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -1716,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1740,12 +1756,12 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
@@ -1755,22 +1771,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
@@ -1808,26 +1824,22 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>161分钟</t>
+          <t>179分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>08:11采样：该车到重点站沪南路华夏西路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数93分钟，约±15分钟</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：10:01采样，终点ETA 4分钟</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
       <c r="N12" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -1835,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1859,12 +1871,12 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
@@ -1874,22 +1886,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>161.0</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>9/27</t>
+          <t>20/27</t>
         </is>
       </c>
     </row>
@@ -1927,26 +1939,22 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>163分钟</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>08:11采样：该车到重点站金杨路云山路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数110分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：09:40采样，终点ETA 6分钟</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
       <c r="N13" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -1954,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1983,7 +1991,7 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
@@ -1993,22 +2001,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>163.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>11/27</t>
+          <t>5/27</t>
         </is>
       </c>
     </row>
@@ -2046,26 +2054,22 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>189分钟</t>
+          <t>171分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>08:01采样：该车到重点站康沈路秀康路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数143分钟，约±8分钟</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：10:01采样，终点ETA 8分钟</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
       <c r="N14" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -2073,7 +2077,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2102,7 +2106,7 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
@@ -2112,22 +2116,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>189.0</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>17/27</t>
+          <t>15/27</t>
         </is>
       </c>
     </row>
@@ -2155,12 +2159,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq38推进至seq55，推进17站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2188,7 +2192,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2196,10 +2200,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q15" s="2" t="inlineStr"/>
-      <c r="R15" s="2" t="inlineStr"/>
-      <c r="S15" s="2" t="inlineStr"/>
-      <c r="T15" s="2" t="inlineStr"/>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>沪南路高科西路</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>08:47</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>08:54</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>到达按末次同向重点站ETA估算；折返发车结合首次反向运行观测取区间中点，约±7分钟；反向重点站沪南路北中路 ETA 4分钟参与校验</t>
+        </is>
+      </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
           <t>07:24</t>
@@ -2217,7 +2237,7 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
@@ -2276,26 +2296,22 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>153分钟</t>
+          <t>150分钟</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>08:11采样：该车到重点站金杨路金业路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数110分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：09:40采样，终点ETA 19分钟</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
       <c r="N16" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -2303,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2332,7 +2348,7 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
@@ -2342,22 +2358,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -2400,21 +2416,17 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>176分钟</t>
+          <t>175分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数176分钟估算，约±13分钟</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：10:21采样，终点ETA 4分钟</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
       <c r="N17" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -2422,7 +2434,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2446,12 +2458,12 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
@@ -2461,22 +2473,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>176.0</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>16/27</t>
+          <t>20/27</t>
         </is>
       </c>
     </row>
@@ -2509,29 +2521,29 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>151分钟</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>08:11采样：该车到重点站金杨路金业路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数111分钟，约±10分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2541,7 +2553,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2565,12 +2577,12 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
@@ -2580,22 +2592,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>5/27</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -2628,29 +2640,29 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>171分钟</t>
+          <t>169分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>07:50采样：该车到重点站关岳路康达路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数160分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2660,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2684,12 +2696,12 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
@@ -2699,22 +2711,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>148.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>12/27</t>
+          <t>16/27</t>
         </is>
       </c>
     </row>
@@ -2747,27 +2759,31 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -2775,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2799,33 +2815,37 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB20" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>136.5</t>
+        </is>
+      </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -2863,26 +2883,22 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>173分钟</t>
+          <t>171分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>08:11采样：该车到重点站川周公路康沈路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数152分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：10:31采样，终点ETA 14分钟</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
       <c r="N21" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -2890,7 +2906,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2919,7 +2935,7 @@
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
@@ -2929,22 +2945,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>173.0</t>
+          <t>152.5</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>14/27</t>
+          <t>19/27</t>
         </is>
       </c>
     </row>
@@ -2977,27 +2993,31 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -3005,7 +3025,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3029,17 +3049,17 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
@@ -3049,13 +3069,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB22" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>12/27</t>
         </is>
       </c>
     </row>
@@ -3093,19 +3117,19 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>168分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：10:31采样，终点ETA 23分钟</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr"/>
@@ -3116,7 +3140,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3140,17 +3164,17 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
@@ -3160,13 +3184,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB23" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>168.0</t>
+        </is>
+      </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>24/27</t>
         </is>
       </c>
     </row>
@@ -3204,19 +3232,19 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>160分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数131分钟估算，约±5分钟</t>
+          <t>10:31采样：该车到重点站五莲路兰城路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数22分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -3231,7 +3259,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3260,7 +3288,7 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
@@ -3280,12 +3308,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>160.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>22/27</t>
         </is>
       </c>
     </row>
@@ -3323,19 +3351,19 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：10:31采样，终点ETA 10分钟</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr"/>
@@ -3346,7 +3374,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3370,17 +3398,17 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
@@ -3390,13 +3418,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB25" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>143.0</t>
+        </is>
+      </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>9/27</t>
         </is>
       </c>
     </row>
@@ -3434,22 +3466,26 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr"/>
+          <t>08:40采样：该车到重点站川周公路康沈路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数128分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3457,7 +3493,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3481,17 +3517,17 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
@@ -3501,13 +3537,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB26" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>10/27</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3565,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -3545,22 +3585,26 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr"/>
+          <t>10:31采样：该车到重点站周东路川周公路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数19分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3568,7 +3612,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3582,7 +3626,7 @@
       <c r="T27" s="2" t="inlineStr"/>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
@@ -3592,17 +3636,17 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
@@ -3612,13 +3656,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB27" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>145.0</t>
+        </is>
+      </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>11/27</t>
         </is>
       </c>
     </row>
@@ -3656,19 +3704,19 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>148分钟</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数148分钟估算，约±5分钟</t>
+          <t>10:21采样：该车到重点站金杨路金口路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数40分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -3683,7 +3731,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3712,7 +3760,7 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
@@ -3732,12 +3780,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
@@ -3755,7 +3803,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -3775,22 +3823,26 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr"/>
+          <t>10:31采样：该车到重点站沪南路御桥路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数42分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3798,7 +3850,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3812,7 +3864,7 @@
       <c r="T29" s="2" t="inlineStr"/>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
@@ -3822,37 +3874,2163 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>148.5</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>16/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>134分钟</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>10:10采样：该车到重点站锦绣路罗山路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数59分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>133.5</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>1/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>135分钟</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>10:31采样：该车到重点站锦绣路罗山路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数58分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>12/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>128分钟</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>10:31采样：该车到重点站沪南路御桥路 ETA 17分钟；叠加该车自身同类时段从该站到终点历史中位数35分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>142.0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>8/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A17590A</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X29" s="2" t="inlineStr">
+      <c r="X33" s="2" t="inlineStr">
         <is>
           <t>证据不足</t>
         </is>
       </c>
-      <c r="Y29" s="2" t="inlineStr">
+      <c r="Y33" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z29" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA29" s="2" t="inlineStr">
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr"/>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB29" s="2" t="inlineStr">
-        <is>
-          <t>159.0</t>
-        </is>
-      </c>
-      <c r="AC29" s="2" t="inlineStr">
-        <is>
-          <t>8/27</t>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>162.0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>23/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>138分钟</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>10:31采样：该车到重点站迎春路长柳路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数74分钟，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>150.5</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>18/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>130分钟</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>10:31采样：该车到重点站浦建路锦绣路 ETA 28分钟；叠加该车自身同类时段从该站到终点历史中位数56分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>146.5</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>14/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>168.0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>24/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>124分钟</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>10:31采样：该车到重点站沪南路华夏西路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数88分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>6/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>129分钟</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>10:31采样：该车到重点站金杨路金业路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数97分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>154.0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>20/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>129分钟</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>10:31采样：该车到重点站川周公路康沈路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数111分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>139.0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>5/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>125分钟</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>10:31采样：该车到重点站金杨路金业路 ETA 20分钟；叠加该车自身同类时段从该站到终点历史中位数93分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>15/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>122分钟</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数122分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>3/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A57051D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>133分钟</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>10:31采样：该车到重点站博兴路兰城路 ETA 25分钟；叠加该车自身同类时段从该站到终点历史中位数106分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>154.0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>20/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>128分钟</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数128分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>148.5</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>16/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>125分钟</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数125分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>133.5</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>1/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>125分钟</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数125分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>136.5</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>4/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>134分钟</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数134分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>152.5</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>19/27</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-16-浦东35路.xlsx
+++ b/data/export/2026-09-16-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC47"/>
+  <dimension ref="A1:AC62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>148.5</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>16/27</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>12/27</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,12 +1065,12 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>8/27</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1308,17 +1308,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>162.0</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>23/27</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>150.5</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>18/27</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1537,22 +1537,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>14/27</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1656,22 +1656,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>168.0</t>
+          <t>146.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>24/27</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1781,12 +1781,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>153.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>20/27</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2011,12 +2011,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>5/27</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -2077,7 +2077,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2126,12 +2126,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>15/27</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -2192,7 +2192,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2247,18 +2247,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2368,12 +2372,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -2434,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2483,12 +2487,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>152.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>20/27</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2592,7 +2596,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2602,12 +2606,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2721,12 +2725,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>148.5</t>
+          <t>146.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>16/27</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2840,12 +2844,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -2878,7 +2882,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2895,10 +2899,14 @@
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：10:31采样，终点ETA 14分钟</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -2906,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2930,12 +2938,12 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
@@ -2960,7 +2968,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>19/27</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -3025,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3064,22 +3072,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>12/27</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -3112,27 +3120,31 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>168分钟</t>
+          <t>167分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：10:31采样，终点ETA 23分钟</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3140,7 +3152,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3164,12 +3176,12 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
@@ -3189,12 +3201,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>168.0</t>
+          <t>167.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>24/27</t>
+          <t>27/29</t>
         </is>
       </c>
     </row>
@@ -3232,26 +3244,22 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>160分钟</t>
+          <t>159分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>10:31采样：该车到重点站五莲路兰城路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数22分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：10:50采样，终点ETA 6分钟</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
       <c r="N24" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -3259,7 +3267,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3288,7 +3296,7 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
@@ -3298,22 +3306,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>22/27</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -3346,27 +3354,31 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>143分钟</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：10:31采样，终点ETA 10分钟</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3374,7 +3386,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3398,12 +3410,12 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
@@ -3413,22 +3425,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>9/27</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -3493,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3547,7 +3559,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>10/27</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -3585,26 +3597,22 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>145分钟</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>10:31采样：该车到重点站周东路川周公路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数19分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：10:40采样，终点ETA 20分钟</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
       <c r="N27" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3612,7 +3620,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3641,7 +3649,7 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
@@ -3651,22 +3659,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>11/27</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -3699,7 +3707,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -3709,14 +3717,14 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>141分钟</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>10:21采样：该车到重点站金杨路金口路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数40分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -3731,7 +3739,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3755,12 +3763,12 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
@@ -3770,22 +3778,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -3823,19 +3831,19 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>138分钟</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>10:31采样：该车到重点站沪南路御桥路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数42分钟，约±5分钟</t>
+          <t>11:01采样：该车到重点站康弘路康丽路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数3分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -3850,7 +3858,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3899,12 +3907,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>148.5</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>16/27</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -3937,7 +3945,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -3954,7 +3962,7 @@
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>10:10采样：该车到重点站锦绣路罗山路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数59分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
@@ -3969,7 +3977,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3993,12 +4001,12 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
@@ -4023,7 +4031,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -4056,24 +4064,24 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>135分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>10:31采样：该车到重点站锦绣路罗山路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数58分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
@@ -4088,7 +4096,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4112,12 +4120,12 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
@@ -4127,22 +4135,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>12/27</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -4175,29 +4183,29 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>10:31采样：该车到重点站沪南路御桥路 ETA 17分钟；叠加该车自身同类时段从该站到终点历史中位数35分钟，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -4207,7 +4215,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4231,12 +4239,12 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
@@ -4246,12 +4254,12 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
@@ -4261,7 +4269,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>8/27</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -4289,12 +4297,12 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq28推进至seq62，推进34站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -4322,7 +4330,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4330,10 +4338,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q33" s="2" t="inlineStr"/>
-      <c r="R33" s="2" t="inlineStr"/>
-      <c r="S33" s="2" t="inlineStr"/>
-      <c r="T33" s="2" t="inlineStr"/>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>迎春路长柳路</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="T33" s="2" t="inlineStr">
+        <is>
+          <t>到达按末次同向重点站ETA估算；折返发车结合首次反向运行观测取区间中点，约±5分钟；反向重点站锦绣路花木路 ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
           <t>09:24</t>
@@ -4351,7 +4375,7 @@
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
@@ -4372,7 +4396,7 @@
       <c r="AB33" s="2" t="inlineStr"/>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -4405,27 +4429,31 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -4433,7 +4461,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4457,17 +4485,17 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
@@ -4477,17 +4505,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>162.0</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>23/27</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -4520,29 +4548,29 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>138分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>10:31采样：该车到重点站迎春路长柳路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数74分钟，约±6分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4552,7 +4580,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4576,12 +4604,12 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
@@ -4601,12 +4629,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>150.5</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>18/27</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -4639,24 +4667,24 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>10:31采样：该车到重点站浦建路锦绣路 ETA 28分钟；叠加该车自身同类时段从该站到终点历史中位数56分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
@@ -4671,7 +4699,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4695,12 +4723,12 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
@@ -4710,22 +4738,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>14/27</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -4763,19 +4791,19 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：11:40采样，终点ETA 9分钟</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr"/>
@@ -4786,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4810,37 +4838,37 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>168.0</t>
+          <t>146.5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>24/27</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -4873,24 +4901,24 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>124分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>10:31采样：该车到重点站沪南路华夏西路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数88分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
@@ -4905,7 +4933,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4929,12 +4957,12 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
@@ -4954,12 +4982,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -4992,24 +5020,24 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>10:31采样：该车到重点站金杨路金业路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数97分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
@@ -5024,7 +5052,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5048,12 +5076,12 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
@@ -5073,12 +5101,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>153.5</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>20/27</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -5111,24 +5139,24 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>10:31采样：该车到重点站川周公路康沈路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数111分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
@@ -5143,7 +5171,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5167,12 +5195,12 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
@@ -5182,7 +5210,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5192,12 +5220,12 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>5/27</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -5230,7 +5258,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -5240,14 +5268,14 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>10:31采样：该车到重点站金杨路金业路 ETA 20分钟；叠加该车自身同类时段从该站到终点历史中位数93分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
@@ -5262,7 +5290,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5286,12 +5314,12 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
@@ -5311,12 +5339,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>15/27</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -5349,29 +5377,29 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>122分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数122分钟估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5381,7 +5409,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5405,12 +5433,12 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
@@ -5430,12 +5458,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -5468,29 +5496,29 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>133分钟</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>10:31采样：该车到重点站博兴路兰城路 ETA 25分钟；叠加该车自身同类时段从该站到终点历史中位数106分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5500,7 +5528,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5524,12 +5552,12 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
@@ -5549,12 +5577,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>152.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>20/27</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -5587,24 +5615,24 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数128分钟估算，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
@@ -5619,7 +5647,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5643,12 +5671,12 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
@@ -5668,12 +5696,12 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>148.5</t>
+          <t>146.5</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>16/27</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -5706,29 +5734,29 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数125分钟估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5738,7 +5766,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5762,12 +5790,12 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
@@ -5777,7 +5805,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5787,12 +5815,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -5830,26 +5858,22 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数125分钟估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：12:40采样，终点ETA 32分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -5857,7 +5881,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5881,12 +5905,12 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
@@ -5906,12 +5930,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -5949,7 +5973,7 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -5961,14 +5985,10 @@
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数134分钟估算，约±10分钟</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：12:40采样，终点ETA 33分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
       <c r="N47" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -5976,7 +5996,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6000,37 +6020,1794 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>末次终点ETA兜底</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>152.5</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>25/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>127分钟</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>12:40采样：该车到重点站金杨路金口路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数41分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
           <t>B</t>
         </is>
       </c>
-      <c r="X47" s="2" t="inlineStr">
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>136.5</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>5/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>127分钟</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>12:40采样：该车到重点站沪南路御桥路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数39分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>143.0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>14/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>133分钟</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>12:40采样：该车到重点站云山路碧云路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数53分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>139.5</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>8/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>135分钟</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>12:40采样：该车到重点站浦建路锦绣路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数67分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>137.5</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>6/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>144分钟</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>12:40采样：该车到重点站锦绣路花木路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数85分钟，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>142.0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>12/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>144分钟</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>12:40采样：该车到重点站金杨路云山路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数104分钟，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>143.0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>14/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>134分钟</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>12:40采样：该车到重点站康沈路秀康路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数107分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>141.3</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>11/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>146.5</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>20/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A79307D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr"/>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>128分钟</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数128分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
         <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y47" s="2" t="inlineStr">
+      <c r="Y57" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z47" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB47" s="2" t="inlineStr">
-        <is>
-          <t>152.5</t>
-        </is>
-      </c>
-      <c r="AC47" s="2" t="inlineStr">
-        <is>
-          <t>19/27</t>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>1/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>7/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>134分钟</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数134分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>4/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>2/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A92076D</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>19/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>136.5</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>5/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-16-浦东35路.xlsx
+++ b/data/export/2026-09-16-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC62"/>
+  <dimension ref="A1:AC95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,14 +708,14 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
           <t>133.5</t>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>144.5</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,14 +1303,14 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
           <t>143.5</t>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,22 +1422,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>142.3</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1537,22 +1537,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1656,22 +1656,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1771,14 +1771,14 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
           <t>142.0</t>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1886,22 +1886,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>153.5</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2001,22 +2001,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>134.3</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -2077,7 +2077,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2116,22 +2116,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -2192,7 +2192,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2247,22 +2247,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>146.5</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2362,14 +2362,14 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
           <t>140.5</t>
@@ -2377,7 +2377,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2477,22 +2477,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>147.7</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2596,22 +2596,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2715,22 +2715,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2834,22 +2834,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2953,22 +2953,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>152.5</t>
+          <t>143.3</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3072,22 +3072,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3191,22 +3191,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>167.0</t>
+          <t>154.5</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>27/29</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -3267,7 +3267,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3306,22 +3306,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>147.3</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3430,17 +3430,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -3505,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3544,22 +3544,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>146.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3659,22 +3659,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>134.7</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -3739,7 +3739,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3778,22 +3778,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3897,22 +3897,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>144.5</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -3977,7 +3977,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4016,14 +4016,14 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
           <t>133.5</t>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -4096,7 +4096,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4135,22 +4135,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -4215,7 +4215,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4254,22 +4254,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4385,7 +4385,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4396,7 +4396,7 @@
       <c r="AB33" s="2" t="inlineStr"/>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -4461,7 +4461,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4500,14 +4500,14 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
           <t>143.5</t>
@@ -4515,7 +4515,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -4580,7 +4580,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4619,22 +4619,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>142.3</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -4699,7 +4699,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4738,22 +4738,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4853,22 +4853,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA37" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4933,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4972,14 +4972,14 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
           <t>142.0</t>
@@ -4987,7 +4987,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -5052,7 +5052,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5091,22 +5091,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>153.5</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -5171,7 +5171,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5210,22 +5210,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>134.3</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -5290,7 +5290,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5329,22 +5329,22 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -5409,7 +5409,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5448,14 +5448,14 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
           <t>140.5</t>
@@ -5463,7 +5463,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5567,22 +5567,22 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>147.7</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -5647,7 +5647,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5686,22 +5686,22 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -5766,7 +5766,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5805,22 +5805,22 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -5853,27 +5853,31 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>133分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：12:40采样，终点ETA 32分钟</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -5881,7 +5885,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5905,12 +5909,12 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
@@ -5920,22 +5924,22 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -5968,27 +5972,31 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：12:40采样，终点ETA 33分钟</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -5996,7 +6004,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6020,12 +6028,12 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
@@ -6035,22 +6043,22 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>152.5</t>
+          <t>143.3</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -6083,24 +6091,24 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>12:40采样：该车到重点站金杨路金口路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数41分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
@@ -6115,7 +6123,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6139,12 +6147,12 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
@@ -6154,22 +6162,22 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -6202,7 +6210,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -6212,19 +6220,19 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>12:40采样：该车到重点站沪南路御桥路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数39分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -6234,7 +6242,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6258,12 +6266,12 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
@@ -6273,22 +6281,22 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>147.3</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -6321,24 +6329,24 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>133分钟</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>12:40采样：该车到重点站云山路碧云路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数53分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
@@ -6353,7 +6361,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6377,12 +6385,12 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
@@ -6392,22 +6400,22 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>134.7</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -6440,24 +6448,24 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>135分钟</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>12:40采样：该车到重点站浦建路锦绣路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数67分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
@@ -6472,7 +6480,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6496,12 +6504,12 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
@@ -6511,22 +6519,22 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -6559,29 +6567,29 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>144分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>12:40采样：该车到重点站锦绣路花木路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数85分钟，约±10分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6591,7 +6599,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6615,12 +6623,12 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
@@ -6630,22 +6638,22 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -6678,29 +6686,29 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>144分钟</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>12:40采样：该车到重点站金杨路云山路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数104分钟，约±10分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6710,7 +6718,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6734,12 +6742,12 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
@@ -6749,22 +6757,22 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA53" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -6797,24 +6805,24 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>12:40采样：该车到重点站康沈路秀康路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数107分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
@@ -6829,7 +6837,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6853,12 +6861,12 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
@@ -6868,22 +6876,22 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -6916,27 +6924,31 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -6944,7 +6956,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6968,37 +6980,37 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA55" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -7026,12 +7038,12 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq59，推进21站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -7059,7 +7071,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7067,10 +7079,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q56" s="2" t="inlineStr"/>
-      <c r="R56" s="2" t="inlineStr"/>
-      <c r="S56" s="2" t="inlineStr"/>
-      <c r="T56" s="2" t="inlineStr"/>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>沪南路高科西路</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="S56" s="2" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="T56" s="2" t="inlineStr">
+        <is>
+          <t>到达按末次同向重点站ETA估算；折返发车结合首次反向运行观测取区间中点，约±9分钟；反向重点站沪南路北中路 ETA 9分钟参与校验</t>
+        </is>
+      </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
           <t>12:30</t>
@@ -7088,7 +7116,7 @@
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
@@ -7109,7 +7137,7 @@
       <c r="AB56" s="2" t="inlineStr"/>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -7142,29 +7170,29 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数128分钟估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -7174,7 +7202,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7198,12 +7226,12 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
@@ -7213,22 +7241,22 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -7261,27 +7289,31 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -7289,7 +7321,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7313,37 +7345,37 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA58" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>134.3</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -7376,29 +7408,29 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数134分钟估算，约±6分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -7408,7 +7440,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7432,12 +7464,12 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
@@ -7447,22 +7479,22 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA59" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>146.5</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -7495,27 +7527,31 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -7523,7 +7559,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7547,37 +7583,37 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA60" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -7610,27 +7646,31 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7638,7 +7678,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7662,17 +7702,17 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
@@ -7682,17 +7722,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -7725,27 +7765,31 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -7753,7 +7797,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7777,37 +7821,3896 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>135.7</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>8/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>130分钟</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>143.3</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>18/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>128分钟</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>134.7</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>7/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A57051D</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>139分钟</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>17:51</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>147.7</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>25/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>16:42</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>127分钟</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>4/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>134分钟</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>17:51</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>15/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>126分钟</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>15:41采样：该车到重点站白桦路明月路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数78分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>9/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>132分钟</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>17:51</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>142.3</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>17/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>17:41</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>136分钟</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>17:51</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>4/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A17590A</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>疑似区间车</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq28推进至seq54，推进26站，达到≥2站确认条件</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>17:51</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>迎春路长柳路</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="S71" s="2" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="T71" s="2" t="inlineStr">
+        <is>
+          <t>到达按末次同向重点站ETA估算；折返发车结合首次反向运行观测取区间中点，约±7分钟；反向重点站锦绣路花木路 ETA 0分钟参与校验</t>
+        </is>
+      </c>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X62" s="2" t="inlineStr">
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr"/>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>—/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>146分钟</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>17:51</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>151.0</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>26/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>18:07</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>142分钟</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>17:51</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>154.5</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>27/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>18:27</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>146分钟</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>17:51采样：该车到重点站五莲路兰城路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数30分钟，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>17:51</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>23/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>149分钟</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS末次终点ETA推算：17:51采样，终点ETA 39分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>17:51</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>末次终点ETA兜底</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>146.5</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>21/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>19:03</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>168分钟</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>17:51采样：该车到重点站沪南路北中路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数72分钟，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>17:51</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>146.5</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>21/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>18:37</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>142分钟</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>17:51采样：该车到重点站金杨路金口路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数38分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>17:51</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>145.0</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>20/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>17:51</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
         <is>
           <t>证据不足</t>
         </is>
       </c>
-      <c r="Y62" s="2" t="inlineStr">
+      <c r="Y78" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z62" s="2" t="inlineStr">
+      <c r="Z78" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA62" s="2" t="inlineStr">
+      <c r="AA78" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB62" s="2" t="inlineStr">
-        <is>
-          <t>136.5</t>
-        </is>
-      </c>
-      <c r="AC62" s="2" t="inlineStr">
-        <is>
-          <t>5/29</t>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>133.5</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>3/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>19:06</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>157分钟</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>17:51采样：该车到重点站迎春路金松路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数72分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>17:51</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>147.3</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>24/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>17:51</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>143.5</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>19/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>17:51</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>131.5</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>2/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>17:51</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>11/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>17:51</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>142.0</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>16/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A57051D</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>17:51</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>147.7</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>25/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>17:51</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>139.0</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>12/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>17:51</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>140.5</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>14/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>17:51</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>134.3</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>6/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>17:51</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>128.7</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>1/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>17:51</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>15/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>17:51</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>135.7</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>8/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>17:51</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>142.3</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>17/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>17:51</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>4/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>17:51</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>139.5</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>13/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>17:51</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>154.5</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>27/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>17:51</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>17:51</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr"/>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>—/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-16-浦东35路.xlsx
+++ b/data/export/2026-09-16-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC95"/>
+  <dimension ref="A1:AC108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,22 +1303,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1427,17 +1427,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>142.3</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1661,17 +1661,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1771,22 +1771,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1886,22 +1886,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2006,17 +2006,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>134.3</t>
+          <t>136.8</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -2077,7 +2077,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2116,22 +2116,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>145.3</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -2192,7 +2192,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2362,22 +2362,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2482,17 +2482,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>147.7</t>
+          <t>150.8</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>28/30</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2601,17 +2601,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>133.8</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2715,22 +2715,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>142.8</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2834,22 +2834,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2953,22 +2953,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>143.3</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3077,17 +3077,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>135.7</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>154.5</t>
+          <t>148.3</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3306,22 +3306,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>147.3</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -3440,7 +3440,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -3505,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3544,22 +3544,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>140.7</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -3739,7 +3739,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3778,22 +3778,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3902,17 +3902,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -3977,7 +3977,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4016,22 +4016,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -4096,7 +4096,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4140,17 +4140,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -4269,7 +4269,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4500,22 +4500,22 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -4580,7 +4580,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4624,17 +4624,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>142.3</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -4753,7 +4753,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4858,17 +4858,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4933,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4972,22 +4972,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -5052,7 +5052,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5091,22 +5091,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -5171,7 +5171,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5215,17 +5215,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>134.3</t>
+          <t>136.8</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -5290,7 +5290,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5329,22 +5329,22 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>145.3</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -5409,7 +5409,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5448,22 +5448,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5572,17 +5572,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>147.7</t>
+          <t>150.8</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>28/30</t>
         </is>
       </c>
     </row>
@@ -5647,7 +5647,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5686,22 +5686,22 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>142.8</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -5766,7 +5766,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5810,17 +5810,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>133.8</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -5885,7 +5885,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5924,22 +5924,22 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6043,22 +6043,22 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>143.3</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -6123,7 +6123,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6167,17 +6167,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>135.7</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -6242,7 +6242,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6281,22 +6281,22 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>147.3</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -6415,7 +6415,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -6480,7 +6480,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6519,22 +6519,22 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -6653,7 +6653,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -6718,7 +6718,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6762,17 +6762,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -6891,7 +6891,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -6956,7 +6956,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7000,17 +7000,17 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -7071,7 +7071,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -7321,7 +7321,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7365,17 +7365,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>134.3</t>
+          <t>136.8</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -7440,7 +7440,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7479,7 +7479,7 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7489,12 +7489,12 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7603,17 +7603,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>133.8</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -7732,7 +7732,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -7797,7 +7797,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7841,17 +7841,17 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>135.7</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -7916,7 +7916,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7955,22 +7955,22 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>143.3</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -8089,7 +8089,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8198,17 +8198,17 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>147.7</t>
+          <t>150.8</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>28/30</t>
         </is>
       </c>
     </row>
@@ -8327,7 +8327,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8436,17 +8436,17 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -8565,7 +8565,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -8630,7 +8630,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8674,17 +8674,17 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>142.3</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -8749,7 +8749,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8803,7 +8803,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -8836,7 +8836,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq28推进至seq54，推进26站，达到≥2站确认条件</t>
+          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq28推进至seq63，推进35站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -8864,7 +8864,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8968,24 +8968,24 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>146分钟</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -8995,7 +8995,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9034,22 +9034,22 @@
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -9087,24 +9087,24 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>142分钟</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9158,12 +9158,12 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>154.5</t>
+          <t>148.3</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
@@ -9201,29 +9201,29 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>146分钟</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>17:51采样：该车到重点站五莲路兰城路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数30分钟，约±6分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -9233,7 +9233,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
@@ -9272,22 +9272,22 @@
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA74" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>145.3</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -9320,7 +9320,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -9337,10 +9337,14 @@
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：17:51采样，终点ETA 39分钟</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9348,7 +9352,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9372,12 +9376,12 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
@@ -9387,22 +9391,22 @@
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>140.7</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -9435,29 +9439,29 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>168分钟</t>
+          <t>157分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>17:51采样：该车到重点站沪南路北中路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数72分钟，约±6分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -9467,7 +9471,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9491,12 +9495,12 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
@@ -9506,7 +9510,7 @@
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA76" s="2" t="inlineStr">
@@ -9516,12 +9520,12 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -9554,24 +9558,24 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>142分钟</t>
+          <t>151分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>17:51采样：该车到重点站金杨路金口路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数38分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
@@ -9586,7 +9590,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9610,12 +9614,12 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
@@ -9625,22 +9629,22 @@
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>142.8</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -9673,27 +9677,31 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:56</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9701,7 +9709,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9725,37 +9733,37 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -9788,7 +9796,7 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -9798,19 +9806,19 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>157分钟</t>
+          <t>156分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>17:51采样：该车到重点站迎春路金松路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数72分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -9820,7 +9828,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9844,12 +9852,12 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
@@ -9859,22 +9867,22 @@
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA79" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>147.3</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -9907,27 +9915,31 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M80" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -9935,7 +9947,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9959,37 +9971,37 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -10022,27 +10034,31 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -10050,7 +10066,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10074,37 +10090,37 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA81" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -10142,19 +10158,19 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>152分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：19:10采样，终点ETA 21分钟</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr"/>
@@ -10165,7 +10181,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10189,17 +10205,17 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z82" s="2" t="inlineStr">
@@ -10209,17 +10225,17 @@
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -10252,27 +10268,31 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:27</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -10280,7 +10300,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10304,37 +10324,37 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z83" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -10367,27 +10387,31 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:55</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>160分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M84" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -10395,7 +10419,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10419,17 +10443,17 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z84" s="2" t="inlineStr">
@@ -10439,17 +10463,17 @@
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>147.7</t>
+          <t>150.8</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>28/30</t>
         </is>
       </c>
     </row>
@@ -10482,27 +10506,31 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:43</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -10510,7 +10538,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10534,17 +10562,17 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z85" s="2" t="inlineStr">
@@ -10554,17 +10582,17 @@
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -10602,19 +10630,19 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:03</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>153分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：19:31采样，终点ETA 32分钟</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr"/>
@@ -10625,7 +10653,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10649,37 +10677,37 @@
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z86" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -10712,27 +10740,31 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:54</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -10740,7 +10772,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10764,17 +10796,17 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z87" s="2" t="inlineStr">
@@ -10784,17 +10816,17 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>134.3</t>
+          <t>136.8</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -10827,27 +10859,31 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M88" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -10855,7 +10891,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10879,17 +10915,17 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z88" s="2" t="inlineStr">
@@ -10899,17 +10935,17 @@
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>133.8</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -10947,19 +10983,19 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:08</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：20:01采样，终点ETA 7分钟</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr"/>
@@ -10970,7 +11006,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10994,17 +11030,17 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z89" s="2" t="inlineStr">
@@ -11014,17 +11050,17 @@
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -11057,27 +11093,31 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>155分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M90" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -11085,7 +11125,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11109,17 +11149,17 @@
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z90" s="2" t="inlineStr">
@@ -11129,17 +11169,17 @@
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>135.7</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -11172,27 +11212,31 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M91" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11200,7 +11244,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11224,17 +11268,17 @@
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z91" s="2" t="inlineStr">
@@ -11244,17 +11288,17 @@
       </c>
       <c r="AA91" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>142.3</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -11315,7 +11359,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11369,7 +11413,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11474,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11469,22 +11513,22 @@
       </c>
       <c r="Z93" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA93" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -11517,27 +11561,31 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:36</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M94" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11545,7 +11593,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11569,17 +11617,17 @@
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
@@ -11589,12 +11637,12 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>154.5</t>
+          <t>148.3</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
@@ -11637,19 +11685,19 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：20:41采样，终点ETA 10分钟</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr"/>
@@ -11660,7 +11708,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11684,33 +11732,1592 @@
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>末次终点ETA兜底</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>1/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>20:59</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>129分钟</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>20:50</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>140.7</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>16/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>21:13</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>133分钟</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS末次终点ETA推算：20:41采样，终点ETA 32分钟</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>20:50</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>末次终点ETA兜底</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>146.8</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>25/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr"/>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>疑似区间车</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>原方向在全程51%处后消失；随后反向物理轨迹由seq28推进至seq44，推进16站，达到≥2站确认条件</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>20:50</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr">
+        <is>
+          <t>迎春路长柳路</t>
+        </is>
+      </c>
+      <c r="R98" s="2" t="inlineStr">
+        <is>
+          <t>20:11</t>
+        </is>
+      </c>
+      <c r="S98" s="2" t="inlineStr">
+        <is>
+          <t>20:16</t>
+        </is>
+      </c>
+      <c r="T98" s="2" t="inlineStr">
+        <is>
+          <t>到达按末次同向重点站ETA估算；折返发车结合首次反向运行观测取区间中点，约±5分钟；反向重点站锦绣路花木路 ETA 0分钟参与校验</t>
+        </is>
+      </c>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X95" s="2" t="inlineStr">
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>26/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr"/>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>21:22</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>128分钟</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS末次终点ETA推算：20:50采样，终点ETA 32分钟</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>20:50</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr"/>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>末次终点ETA兜底</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>135.2</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>7/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr"/>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>20:50</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr"/>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
         <is>
           <t>证据不足</t>
         </is>
       </c>
-      <c r="Y95" s="2" t="inlineStr">
+      <c r="Y100" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z95" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA95" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB95" s="2" t="inlineStr"/>
-      <c r="AC95" s="2" t="inlineStr">
-        <is>
-          <t>—/30</t>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>145.3</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>24/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr"/>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr"/>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>20:41</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr"/>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V101" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W101" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z101" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr">
+        <is>
+          <t>17/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr"/>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>疑似区间车</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq28推进至seq30，推进2站，达到≥2站确认条件</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr"/>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>20:50</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr">
+        <is>
+          <t>迎春路长柳路</t>
+        </is>
+      </c>
+      <c r="R102" s="2" t="inlineStr">
+        <is>
+          <t>20:28</t>
+        </is>
+      </c>
+      <c r="S102" s="2" t="inlineStr">
+        <is>
+          <t>20:34</t>
+        </is>
+      </c>
+      <c r="T102" s="2" t="inlineStr">
+        <is>
+          <t>到达按末次同向重点站ETA估算；折返发车结合首次反向运行观测取区间中点，约±6分钟；反向重点站锦绣路花木路 ETA 0分钟参与校验</t>
+        </is>
+      </c>
+      <c r="U102" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z102" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA102" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB102" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
+      <c r="AC102" s="2" t="inlineStr">
+        <is>
+          <t>8/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr"/>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>21:32</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>113分钟</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>20:50采样：该车到重点站云山路碧云路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数38分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>20:50</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr"/>
+      <c r="R103" s="2" t="inlineStr"/>
+      <c r="S103" s="2" t="inlineStr"/>
+      <c r="T103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V103" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W103" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X103" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y103" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z103" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA103" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB103" s="2" t="inlineStr">
+        <is>
+          <t>136.5</t>
+        </is>
+      </c>
+      <c r="AC103" s="2" t="inlineStr">
+        <is>
+          <t>10/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr"/>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>21:46</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>127分钟</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr"/>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>20:50采样：该车到重点站沪南路北中路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数49分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>20:50</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q104" s="2" t="inlineStr"/>
+      <c r="R104" s="2" t="inlineStr"/>
+      <c r="S104" s="2" t="inlineStr"/>
+      <c r="T104" s="2" t="inlineStr"/>
+      <c r="U104" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V104" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W104" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X104" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y104" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z104" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA104" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB104" s="2" t="inlineStr">
+        <is>
+          <t>142.8</t>
+        </is>
+      </c>
+      <c r="AC104" s="2" t="inlineStr">
+        <is>
+          <t>22/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr"/>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>22:03</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>124分钟</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr"/>
+      <c r="K105" s="2" t="inlineStr"/>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>20:50采样：该车到重点站丁香路锦绣路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数71分钟，约±9分钟</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>20:50</t>
+        </is>
+      </c>
+      <c r="P105" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q105" s="2" t="inlineStr"/>
+      <c r="R105" s="2" t="inlineStr"/>
+      <c r="S105" s="2" t="inlineStr"/>
+      <c r="T105" s="2" t="inlineStr"/>
+      <c r="U105" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="V105" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W105" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X105" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y105" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z105" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA105" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB105" s="2" t="inlineStr">
+        <is>
+          <t>138.5</t>
+        </is>
+      </c>
+      <c r="AC105" s="2" t="inlineStr">
+        <is>
+          <t>13/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr"/>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>22:11</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>127分钟</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr"/>
+      <c r="K106" s="2" t="inlineStr"/>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>20:50采样：该车到重点站沪南路高科西路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数78分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>20:50</t>
+        </is>
+      </c>
+      <c r="P106" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q106" s="2" t="inlineStr"/>
+      <c r="R106" s="2" t="inlineStr"/>
+      <c r="S106" s="2" t="inlineStr"/>
+      <c r="T106" s="2" t="inlineStr"/>
+      <c r="U106" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="V106" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W106" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X106" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y106" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z106" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA106" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB106" s="2" t="inlineStr">
+        <is>
+          <t>139.5</t>
+        </is>
+      </c>
+      <c r="AC106" s="2" t="inlineStr">
+        <is>
+          <t>14/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr"/>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>22:42</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>132分钟</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr"/>
+      <c r="K107" s="2" t="inlineStr"/>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>20:50采样：该车到重点站川周公路康沈路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数109分钟，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>20:50</t>
+        </is>
+      </c>
+      <c r="P107" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q107" s="2" t="inlineStr"/>
+      <c r="R107" s="2" t="inlineStr"/>
+      <c r="S107" s="2" t="inlineStr"/>
+      <c r="T107" s="2" t="inlineStr"/>
+      <c r="U107" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="V107" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W107" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X107" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y107" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z107" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA107" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB107" s="2" t="inlineStr">
+        <is>
+          <t>141.5</t>
+        </is>
+      </c>
+      <c r="AC107" s="2" t="inlineStr">
+        <is>
+          <t>19/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr"/>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>23:01</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>126分钟</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr"/>
+      <c r="K108" s="2" t="inlineStr"/>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数126分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N108" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>20:50</t>
+        </is>
+      </c>
+      <c r="P108" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q108" s="2" t="inlineStr"/>
+      <c r="R108" s="2" t="inlineStr"/>
+      <c r="S108" s="2" t="inlineStr"/>
+      <c r="T108" s="2" t="inlineStr"/>
+      <c r="U108" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="V108" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W108" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X108" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y108" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z108" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA108" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB108" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
+      <c r="AC108" s="2" t="inlineStr">
+        <is>
+          <t>6/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-16-浦东35路.xlsx
+++ b/data/export/2026-09-16-浦东35路.xlsx
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>135.2</t>
+          <t>134.2</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>146.2</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -2077,7 +2077,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2121,17 +2121,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>145.3</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -2611,7 +2611,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2725,12 +2725,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>142.8</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2844,12 +2844,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2963,7 +2963,7 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>139.8</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -3739,7 +3739,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -3977,7 +3977,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>135.2</t>
+          <t>134.2</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -4150,7 +4150,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -4269,7 +4269,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -4461,7 +4461,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4510,12 +4510,12 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -4634,7 +4634,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4933,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4982,7 +4982,7 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>146.2</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5225,7 +5225,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -5290,7 +5290,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5334,17 +5334,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>145.3</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -5409,7 +5409,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5458,12 +5458,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -5647,7 +5647,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5696,12 +5696,12 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>142.8</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -5885,7 +5885,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6053,7 +6053,7 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>139.8</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6242,7 +6242,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6415,7 +6415,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -6480,7 +6480,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6653,7 +6653,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -6772,7 +6772,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -7256,7 +7256,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -7375,7 +7375,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -7613,7 +7613,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -7732,7 +7732,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -7916,7 +7916,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7965,7 +7965,7 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>139.8</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -8089,7 +8089,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -8327,7 +8327,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -8684,7 +8684,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -8803,7 +8803,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -8995,7 +8995,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9044,7 +9044,7 @@
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>146.2</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
@@ -9233,7 +9233,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9277,17 +9277,17 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>145.3</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -9590,7 +9590,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9639,12 +9639,12 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>142.8</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -9709,7 +9709,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9758,12 +9758,12 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>135.2</t>
+          <t>134.2</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -9828,7 +9828,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9947,7 +9947,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -10066,7 +10066,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10235,7 +10235,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -10300,7 +10300,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10349,7 +10349,7 @@
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
@@ -10653,7 +10653,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10702,12 +10702,12 @@
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -10826,7 +10826,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -10945,7 +10945,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -11060,7 +11060,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -11298,7 +11298,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -11413,7 +11413,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -11474,7 +11474,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11523,12 +11523,12 @@
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -11914,27 +11914,31 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>133分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：20:41采样，终点ETA 32分钟</t>
-        </is>
-      </c>
-      <c r="M97" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -11942,7 +11946,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11966,12 +11970,12 @@
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
@@ -11991,7 +11995,7 @@
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>146.2</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
@@ -12029,7 +12033,7 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程51%处后消失；随后反向物理轨迹由seq28推进至seq44，推进16站，达到≥2站确认条件</t>
+          <t>原方向在全程51%处后消失；随后反向物理轨迹由seq28推进至seq62，推进34站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -12057,7 +12061,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12160,27 +12164,31 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:19</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：20:50采样，终点ETA 32分钟</t>
-        </is>
-      </c>
-      <c r="M99" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -12188,7 +12196,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12212,12 +12220,12 @@
       </c>
       <c r="W99" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X99" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y99" s="2" t="inlineStr">
@@ -12237,12 +12245,12 @@
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>135.2</t>
+          <t>134.2</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -12275,27 +12283,31 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:29</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M100" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -12303,7 +12315,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12327,17 +12339,17 @@
       </c>
       <c r="W100" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X100" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y100" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z100" s="2" t="inlineStr">
@@ -12347,17 +12359,17 @@
       </c>
       <c r="AA100" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB100" s="2" t="inlineStr">
         <is>
-          <t>145.3</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -12505,7 +12517,7 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq28推进至seq30，推进2站，达到≥2站确认条件</t>
+          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq28推进至seq48，推进20站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -12533,7 +12545,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12641,26 +12653,22 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>21:32</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>113分钟</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr"/>
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>20:50采样：该车到重点站云山路碧云路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数38分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M103" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：21:20采样，终点ETA 22分钟</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr"/>
       <c r="N103" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -12668,7 +12676,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12692,12 +12700,12 @@
       </c>
       <c r="W103" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X103" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y103" s="2" t="inlineStr">
@@ -12717,12 +12725,12 @@
       </c>
       <c r="AB103" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -12760,26 +12768,22 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>21:46</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr"/>
       <c r="K104" s="2" t="inlineStr"/>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>20:50采样：该车到重点站沪南路北中路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数49分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M104" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：21:20采样，终点ETA 25分钟</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr"/>
       <c r="N104" s="2" t="inlineStr">
         <is>
           <t>07:10</t>
@@ -12787,7 +12791,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12811,12 +12815,12 @@
       </c>
       <c r="W104" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X104" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y104" s="2" t="inlineStr">
@@ -12836,12 +12840,12 @@
       </c>
       <c r="AB104" s="2" t="inlineStr">
         <is>
-          <t>142.8</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC104" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -12879,24 +12883,24 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>22:03</t>
+          <t>22:09</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>124分钟</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr"/>
       <c r="K105" s="2" t="inlineStr"/>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>20:50采样：该车到重点站丁香路锦绣路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数71分钟，约±9分钟</t>
+          <t>21:20采样：该车到重点站沪南路北中路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数48分钟，约±10分钟</t>
         </is>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr">
@@ -12906,7 +12910,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12955,7 +12959,7 @@
       </c>
       <c r="AB105" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>139.8</t>
         </is>
       </c>
       <c r="AC105" s="2" t="inlineStr">
@@ -12998,19 +13002,19 @@
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>22:11</t>
+          <t>22:13</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr"/>
       <c r="K106" s="2" t="inlineStr"/>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>20:50采样：该车到重点站沪南路高科西路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数78分钟，约±5分钟</t>
+          <t>21:20采样：该车到重点站云山路碧云路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数50分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M106" s="2" t="inlineStr">
@@ -13025,7 +13029,7 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
@@ -13074,7 +13078,7 @@
       </c>
       <c r="AB106" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC106" s="2" t="inlineStr">
@@ -13117,24 +13121,24 @@
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>22:42</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J107" s="2" t="inlineStr"/>
       <c r="K107" s="2" t="inlineStr"/>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>20:50采样：该车到重点站川周公路康沈路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数109分钟，约±6分钟</t>
+          <t>21:20采样：该车到重点站沪南路高科西路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数80分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N107" s="2" t="inlineStr">
@@ -13144,7 +13148,7 @@
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P107" s="2" t="inlineStr">
@@ -13193,12 +13197,12 @@
       </c>
       <c r="AB107" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AC107" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -13236,24 +13240,24 @@
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>22:55</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>126分钟</t>
+          <t>121分钟</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr"/>
       <c r="K108" s="2" t="inlineStr"/>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数126分钟估算，约±5分钟</t>
+          <t>21:20采样：该车到重点站沪南路华夏西路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数86分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
@@ -13263,7 +13267,7 @@
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P108" s="2" t="inlineStr">
@@ -13292,7 +13296,7 @@
       </c>
       <c r="X108" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y108" s="2" t="inlineStr">
@@ -13312,12 +13316,12 @@
       </c>
       <c r="AB108" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC108" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-16-浦东35路.xlsx
+++ b/data/export/2026-09-16-浦东35路.xlsx
@@ -446,7 +446,7 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
     <col width="36" customWidth="1" min="20" max="20"/>
@@ -1151,14 +1151,18 @@
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>迎春路长柳路</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr"/>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>07:43</t>
+        </is>
+      </c>
       <c r="S6" s="2" t="inlineStr"/>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>区间折返已由主分类器确认；现有采样不足以把折返发车时间控制在±10分钟</t>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq24映射；现有采样不足以把折返发车时间控制在±10分钟</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1264,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1313,7 +1317,7 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1671,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1781,12 +1785,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>139.8</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -2131,7 +2135,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2206,7 @@
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>沪南路高科西路</t>
+          <t>物理seq23（站名待映射）</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
@@ -2217,7 +2221,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>到达按末次同向重点站ETA估算；折返发车结合首次反向运行观测取区间中点，约±7分钟；反向重点站沪南路北中路 ETA 4分钟参与校验</t>
+          <t>折返点按重建物理位置seq23映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±7分钟；反向位置物理seq38（站名待映射） ETA 4分钟参与校验</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2262,7 +2266,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -2323,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2372,12 +2376,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>141.2</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2795,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2844,7 +2848,7 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>131.7</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2914,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2963,12 +2967,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>139.8</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -3087,7 +3091,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -3739,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -4340,7 +4344,7 @@
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t>迎春路长柳路</t>
+          <t>物理seq32（站名待映射）</t>
         </is>
       </c>
       <c r="R33" s="2" t="inlineStr">
@@ -4355,7 +4359,7 @@
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>到达按末次同向重点站ETA估算；折返发车结合首次反向运行观测取区间中点，约±5分钟；反向重点站锦绣路花木路 ETA 0分钟参与校验</t>
+          <t>折返点按重建物理位置seq32映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±5分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4461,7 +4465,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4510,7 +4514,7 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4868,7 +4872,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4982,12 +4986,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>139.8</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -5344,7 +5348,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -5409,7 +5413,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5458,12 +5462,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>141.2</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -5647,7 +5651,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5885,7 +5889,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5934,7 +5938,7 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>131.7</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
@@ -6004,7 +6008,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6053,12 +6057,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>139.8</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -6177,7 +6181,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -6480,7 +6484,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -7010,7 +7014,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -7081,7 +7085,7 @@
       </c>
       <c r="Q56" s="2" t="inlineStr">
         <is>
-          <t>沪南路高科西路</t>
+          <t>物理seq24（站名待映射）</t>
         </is>
       </c>
       <c r="R56" s="2" t="inlineStr">
@@ -7096,7 +7100,7 @@
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>到达按末次同向重点站ETA估算；折返发车结合首次反向运行观测取区间中点，约±9分钟；反向重点站沪南路北中路 ETA 9分钟参与校验</t>
+          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq38（站名待映射） ETA 9分钟参与校验</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -7494,7 +7498,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -7851,7 +7855,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -7916,7 +7920,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7965,12 +7969,12 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>139.8</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -8874,22 +8878,22 @@
       </c>
       <c r="Q71" s="2" t="inlineStr">
         <is>
-          <t>迎春路长柳路</t>
+          <t>物理seq28（站名待映射）</t>
         </is>
       </c>
       <c r="R71" s="2" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="S71" s="2" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="T71" s="2" t="inlineStr">
         <is>
-          <t>到达按末次同向重点站ETA估算；折返发车结合首次反向运行观测取区间中点，约±7分钟；反向重点站锦绣路花木路 ETA 0分钟参与校验</t>
+          <t>折返点按重建物理位置seq28映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
         </is>
       </c>
       <c r="U71" s="2" t="inlineStr">
@@ -9287,7 +9291,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -9525,7 +9529,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -9590,7 +9594,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9947,7 +9951,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9996,7 +10000,7 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
@@ -10066,7 +10070,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10300,7 +10304,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10349,12 +10353,12 @@
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>139.8</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -10592,7 +10596,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -10653,7 +10657,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10702,12 +10706,12 @@
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>141.2</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -11179,7 +11183,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -11474,7 +11478,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11523,7 +11527,7 @@
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>131.7</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
@@ -12086,7 +12090,7 @@
       </c>
       <c r="T98" s="2" t="inlineStr">
         <is>
-          <t>到达按末次同向重点站ETA估算；折返发车结合首次反向运行观测取区间中点，约±5分钟；反向重点站锦绣路花木路 ETA 0分钟参与校验</t>
+          <t>折返点按重建物理位置seq33映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±5分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
         </is>
       </c>
       <c r="U98" s="2" t="inlineStr">
@@ -12369,7 +12373,7 @@
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -12484,7 +12488,7 @@
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -12517,7 +12521,7 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq28推进至seq48，推进20站，达到≥2站确认条件</t>
+          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq28推进至seq54，推进26站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -12545,7 +12549,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12555,22 +12559,22 @@
       </c>
       <c r="Q102" s="2" t="inlineStr">
         <is>
-          <t>迎春路长柳路</t>
+          <t>物理seq27（站名待映射）</t>
         </is>
       </c>
       <c r="R102" s="2" t="inlineStr">
         <is>
-          <t>20:28</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="S102" s="2" t="inlineStr">
         <is>
-          <t>20:34</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="T102" s="2" t="inlineStr">
         <is>
-          <t>到达按末次同向重点站ETA估算；折返发车结合首次反向运行观测取区间中点，约±6分钟；反向重点站锦绣路花木路 ETA 0分钟参与校验</t>
+          <t>折返点按重建物理位置seq27映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
         </is>
       </c>
       <c r="U102" s="2" t="inlineStr">
@@ -12648,27 +12652,31 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>21:42</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>123分钟</t>
+          <t>121分钟</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr"/>
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：21:20采样，终点ETA 22分钟</t>
-        </is>
-      </c>
-      <c r="M103" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N103" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -12676,7 +12684,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12700,12 +12708,12 @@
       </c>
       <c r="W103" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X103" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y103" s="2" t="inlineStr">
@@ -12725,7 +12733,7 @@
       </c>
       <c r="AB103" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC103" s="2" t="inlineStr">
@@ -12763,12 +12771,12 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>21:46</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
@@ -12780,10 +12788,14 @@
       <c r="K104" s="2" t="inlineStr"/>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：21:20采样，终点ETA 25分钟</t>
-        </is>
-      </c>
-      <c r="M104" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N104" s="2" t="inlineStr">
         <is>
           <t>07:10</t>
@@ -12791,7 +12803,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12815,12 +12827,12 @@
       </c>
       <c r="W104" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X104" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y104" s="2" t="inlineStr">
@@ -12883,26 +12895,22 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>22:09</t>
+          <t>22:12</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr"/>
       <c r="K105" s="2" t="inlineStr"/>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>21:20采样：该车到重点站沪南路北中路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数48分钟，约±10分钟</t>
-        </is>
-      </c>
-      <c r="M105" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：21:31采样，终点ETA 41分钟</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr"/>
       <c r="N105" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -12910,7 +12918,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12934,12 +12942,12 @@
       </c>
       <c r="W105" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X105" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y105" s="2" t="inlineStr">
@@ -12959,12 +12967,12 @@
       </c>
       <c r="AB105" s="2" t="inlineStr">
         <is>
-          <t>139.8</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC105" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -13007,14 +13015,14 @@
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr"/>
       <c r="K106" s="2" t="inlineStr"/>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>21:20采样：该车到重点站云山路碧云路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数50分钟，约±5分钟</t>
+          <t>21:31采样：该车到重点站长岛路张杨北路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数35分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M106" s="2" t="inlineStr">
@@ -13029,7 +13037,7 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
@@ -13078,12 +13086,12 @@
       </c>
       <c r="AB106" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>139.8</t>
         </is>
       </c>
       <c r="AC106" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -13121,24 +13129,24 @@
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>22:39</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J107" s="2" t="inlineStr"/>
       <c r="K107" s="2" t="inlineStr"/>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>21:20采样：该车到重点站沪南路高科西路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数80分钟，约±7分钟</t>
+          <t>21:31采样：该车到重点站锦绣路花木路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数68分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N107" s="2" t="inlineStr">
@@ -13148,7 +13156,7 @@
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P107" s="2" t="inlineStr">
@@ -13197,12 +13205,12 @@
       </c>
       <c r="AB107" s="2" t="inlineStr">
         <is>
-          <t>141.2</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="AC107" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -13240,19 +13248,19 @@
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>22:55</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>121分钟</t>
+          <t>116分钟</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr"/>
       <c r="K108" s="2" t="inlineStr"/>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>21:20采样：该车到重点站沪南路华夏西路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数86分钟，约±6分钟</t>
+          <t>21:31采样：该车到重点站沪南路高科西路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数72分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M108" s="2" t="inlineStr">
@@ -13267,7 +13275,7 @@
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P108" s="2" t="inlineStr">
@@ -13316,7 +13324,7 @@
       </c>
       <c r="AB108" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>131.7</t>
         </is>
       </c>
       <c r="AC108" s="2" t="inlineStr">

--- a/data/export/2026-09-16-浦东35路.xlsx
+++ b/data/export/2026-09-16-浦东35路.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1785,12 +1785,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>139.8</t>
+          <t>138.8</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>140.8</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>131.7</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2967,7 +2967,7 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>140.2</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -4465,7 +4465,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4514,12 +4514,12 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>139.8</t>
+          <t>138.8</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5462,7 +5462,7 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>140.8</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -5889,7 +5889,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>131.7</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6057,7 +6057,7 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>140.2</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6181,7 +6181,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -6484,7 +6484,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6657,7 +6657,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -7260,7 +7260,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -7498,7 +7498,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -7855,7 +7855,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -7920,7 +7920,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7969,7 +7969,7 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>140.2</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -8331,7 +8331,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -8807,7 +8807,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -9529,7 +9529,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -9594,7 +9594,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9951,7 +9951,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10000,12 +10000,12 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -10070,7 +10070,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10353,12 +10353,12 @@
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>139.8</t>
+          <t>138.8</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -10657,7 +10657,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10706,7 +10706,7 @@
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>140.8</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
@@ -10949,7 +10949,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -11183,7 +11183,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -11417,7 +11417,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -11478,7 +11478,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11527,12 +11527,12 @@
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>131.7</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -12488,7 +12488,7 @@
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -12521,7 +12521,7 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq28推进至seq54，推进26站，达到≥2站确认条件</t>
+          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq28推进至seq59，推进31站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -12549,7 +12549,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12657,24 +12657,24 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>21:41</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>121分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr"/>
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr">
@@ -12684,7 +12684,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12733,12 +12733,12 @@
       </c>
       <c r="AB103" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -12803,7 +12803,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12890,27 +12890,31 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>22:12</t>
+          <t>22:11</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr"/>
       <c r="K105" s="2" t="inlineStr"/>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：21:31采样，终点ETA 41分钟</t>
-        </is>
-      </c>
-      <c r="M105" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N105" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -12918,7 +12922,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12942,12 +12946,12 @@
       </c>
       <c r="W105" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X105" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y105" s="2" t="inlineStr">
@@ -12967,7 +12971,7 @@
       </c>
       <c r="AB105" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>140.2</t>
         </is>
       </c>
       <c r="AC105" s="2" t="inlineStr">
@@ -13010,19 +13014,19 @@
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>22:13</t>
+          <t>22:08</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr"/>
       <c r="K106" s="2" t="inlineStr"/>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>21:31采样：该车到重点站长岛路张杨北路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数35分钟，约±5分钟</t>
+          <t>21:50采样：该车到重点站东波路莱阳路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数16分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M106" s="2" t="inlineStr">
@@ -13037,7 +13041,7 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
@@ -13086,12 +13090,12 @@
       </c>
       <c r="AB106" s="2" t="inlineStr">
         <is>
-          <t>139.8</t>
+          <t>138.8</t>
         </is>
       </c>
       <c r="AC106" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -13134,14 +13138,14 @@
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J107" s="2" t="inlineStr"/>
       <c r="K107" s="2" t="inlineStr"/>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>21:31采样：该车到重点站锦绣路花木路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数68分钟，约±5分钟</t>
+          <t>21:50采样：该车到重点站云山路碧云路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数47分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M107" s="2" t="inlineStr">
@@ -13156,7 +13160,7 @@
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P107" s="2" t="inlineStr">
@@ -13205,7 +13209,7 @@
       </c>
       <c r="AB107" s="2" t="inlineStr">
         <is>
-          <t>140.8</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC107" s="2" t="inlineStr">
@@ -13248,24 +13252,24 @@
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>116分钟</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr"/>
       <c r="K108" s="2" t="inlineStr"/>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>21:31采样：该车到重点站沪南路高科西路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数72分钟，约±6分钟</t>
+          <t>21:50采样：该车到重点站迎春路金松路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数64分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
@@ -13275,7 +13279,7 @@
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P108" s="2" t="inlineStr">
@@ -13324,12 +13328,12 @@
       </c>
       <c r="AB108" s="2" t="inlineStr">
         <is>
-          <t>131.7</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC108" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
